--- a/260513_Betonartikel/Results/Members_continuous_rc_rec_150_clean.xlsx
+++ b/260513_Betonartikel/Results/Members_continuous_rc_rec_150_clean.xlsx
@@ -504,7 +504,7 @@
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>system</t>
+          <t>Statisches System</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T2" t="n">
@@ -727,7 +727,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T3" t="n">
@@ -828,7 +828,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T4" t="n">
@@ -929,7 +929,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T5" t="n">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T6" t="n">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T7" t="n">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T8" t="n">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T9" t="n">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T10" t="n">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T11" t="n">
@@ -1636,7 +1636,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T12" t="n">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T13" t="n">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T14" t="n">
@@ -1939,7 +1939,7 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T15" t="n">
@@ -2040,7 +2040,7 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T16" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T17" t="n">
@@ -2242,7 +2242,7 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T18" t="n">
@@ -2343,7 +2343,7 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T19" t="n">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T20" t="n">
@@ -2545,7 +2545,7 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T21" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T22" t="n">
@@ -2747,7 +2747,7 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T23" t="n">
@@ -2848,7 +2848,7 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T24" t="n">
@@ -2949,7 +2949,7 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T25" t="n">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T26" t="n">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T27" t="n">
@@ -3252,7 +3252,7 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T28" t="n">
@@ -3353,7 +3353,7 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T29" t="n">
@@ -3454,7 +3454,7 @@
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T30" t="n">
@@ -3555,7 +3555,7 @@
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T31" t="n">
@@ -3656,7 +3656,7 @@
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T32" t="n">
@@ -3757,7 +3757,7 @@
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T33" t="n">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T34" t="n">
@@ -3959,7 +3959,7 @@
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T35" t="n">
@@ -4060,7 +4060,7 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T36" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T37" t="n">
@@ -4262,7 +4262,7 @@
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T38" t="n">
@@ -4363,7 +4363,7 @@
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T39" t="n">
@@ -4464,7 +4464,7 @@
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T40" t="n">
@@ -4565,7 +4565,7 @@
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T41" t="n">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T42" t="n">
@@ -4767,7 +4767,7 @@
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T43" t="n">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T44" t="n">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T45" t="n">
@@ -5070,7 +5070,7 @@
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T46" t="n">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T47" t="n">
@@ -5272,7 +5272,7 @@
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T48" t="n">
@@ -5373,7 +5373,7 @@
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T49" t="n">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T50" t="n">
@@ -5575,7 +5575,7 @@
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T51" t="n">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T52" t="n">
@@ -5777,7 +5777,7 @@
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T53" t="n">
@@ -5878,7 +5878,7 @@
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T54" t="n">
@@ -5979,7 +5979,7 @@
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T55" t="n">
@@ -6080,7 +6080,7 @@
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T56" t="n">
@@ -6181,7 +6181,7 @@
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T57" t="n">
@@ -6282,7 +6282,7 @@
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T58" t="n">
@@ -6383,7 +6383,7 @@
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T59" t="n">
@@ -6484,7 +6484,7 @@
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T60" t="n">
@@ -6585,7 +6585,7 @@
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T61" t="n">
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T62" t="n">
@@ -6787,7 +6787,7 @@
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T63" t="n">
@@ -6888,7 +6888,7 @@
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T64" t="n">
@@ -6989,7 +6989,7 @@
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T65" t="n">
@@ -7090,7 +7090,7 @@
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T66" t="n">
@@ -7191,7 +7191,7 @@
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T67" t="n">
@@ -7292,7 +7292,7 @@
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T68" t="n">
@@ -7393,7 +7393,7 @@
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T69" t="n">
@@ -7494,7 +7494,7 @@
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T70" t="n">
@@ -7595,7 +7595,7 @@
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T71" t="n">
@@ -7696,7 +7696,7 @@
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T72" t="n">
@@ -7797,7 +7797,7 @@
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T73" t="n">
@@ -7898,7 +7898,7 @@
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T74" t="n">
@@ -7999,7 +7999,7 @@
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T75" t="n">
@@ -8100,7 +8100,7 @@
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T76" t="n">
@@ -8201,7 +8201,7 @@
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T77" t="n">
@@ -8302,7 +8302,7 @@
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T78" t="n">
@@ -8403,7 +8403,7 @@
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T79" t="n">
@@ -8504,7 +8504,7 @@
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T80" t="n">
@@ -8605,7 +8605,7 @@
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T81" t="n">
@@ -8706,7 +8706,7 @@
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T82" t="n">
@@ -8807,7 +8807,7 @@
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T83" t="n">
@@ -8908,7 +8908,7 @@
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T84" t="n">
@@ -9009,7 +9009,7 @@
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T85" t="n">
@@ -9110,7 +9110,7 @@
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T86" t="n">
@@ -9211,7 +9211,7 @@
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T87" t="n">
@@ -9312,7 +9312,7 @@
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T88" t="n">
@@ -9413,7 +9413,7 @@
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T89" t="n">
@@ -9514,7 +9514,7 @@
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T90" t="n">
@@ -9615,7 +9615,7 @@
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T91" t="n">
@@ -9716,7 +9716,7 @@
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T92" t="n">
@@ -9817,7 +9817,7 @@
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T93" t="n">
@@ -9918,7 +9918,7 @@
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T94" t="n">
@@ -10019,7 +10019,7 @@
       </c>
       <c r="S95" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T95" t="n">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T96" t="n">
@@ -10221,7 +10221,7 @@
       </c>
       <c r="S97" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T97" t="n">
@@ -10322,7 +10322,7 @@
       </c>
       <c r="S98" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T98" t="n">
@@ -10423,7 +10423,7 @@
       </c>
       <c r="S99" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T99" t="n">
@@ -10524,7 +10524,7 @@
       </c>
       <c r="S100" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T100" t="n">
@@ -10625,7 +10625,7 @@
       </c>
       <c r="S101" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T101" t="n">
@@ -10726,7 +10726,7 @@
       </c>
       <c r="S102" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T102" t="n">
@@ -10827,7 +10827,7 @@
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T103" t="n">
@@ -10928,7 +10928,7 @@
       </c>
       <c r="S104" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T104" t="n">
@@ -11029,7 +11029,7 @@
       </c>
       <c r="S105" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T105" t="n">
@@ -11130,7 +11130,7 @@
       </c>
       <c r="S106" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T106" t="n">
@@ -11231,7 +11231,7 @@
       </c>
       <c r="S107" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T107" t="n">
@@ -11332,7 +11332,7 @@
       </c>
       <c r="S108" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T108" t="n">
@@ -11433,7 +11433,7 @@
       </c>
       <c r="S109" t="inlineStr">
         <is>
-          <t>Bodenaufbau_RCDecke</t>
+          <t>RC_Std</t>
         </is>
       </c>
       <c r="T109" t="n">
